--- a/desktop/templates/nakladna-vymoga.xlsx
+++ b/desktop/templates/nakladna-vymoga.xlsx
@@ -1326,11 +1326,7 @@
       <c r="F4" s="14" t="n"/>
     </row>
     <row r="5" customFormat="1" s="25">
-      <c r="A5" s="84" t="inlineStr">
-        <is>
-          <t>Військова частина</t>
-        </is>
-      </c>
+      <c r="A5" s="84"/>
     </row>
     <row r="6" customFormat="1" s="25">
       <c r="A6" s="85" t="inlineStr">
@@ -1362,11 +1358,7 @@
       </c>
     </row>
     <row r="10" customFormat="1" s="25">
-      <c r="A10" s="83" t="inlineStr">
-        <is>
-          <t>Накладна (вимога) №1/тз</t>
-        </is>
-      </c>
+      <c r="A10" s="83"/>
     </row>
     <row r="11" customFormat="1" s="25">
       <c r="A11" s="85" t="n"/>
@@ -1401,9 +1393,7 @@
           <t>Дата операції:</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>45891</v>
-      </c>
+      <c r="B15" s="10"/>
       <c r="C15" s="14" t="n"/>
       <c r="D15" s="14" t="n"/>
       <c r="E15" s="85" t="inlineStr">
@@ -1422,19 +1412,11 @@
       <c r="B16" s="23" t="n"/>
       <c r="C16" s="14" t="n"/>
       <c r="D16" s="14" t="n"/>
-      <c r="E16" s="85" t="inlineStr">
-        <is>
-          <t>Підстава (мета): Забезпечення</t>
-        </is>
-      </c>
+      <c r="E16" s="85"/>
       <c r="F16" s="14" t="n"/>
     </row>
     <row r="17" customFormat="1" s="25">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t>Відповідальний одержувач:</t>
-        </is>
-      </c>
+      <c r="A17" s="85"/>
       <c r="B17" s="23" t="n"/>
       <c r="C17" s="14" t="n"/>
       <c r="D17" s="14" t="n"/>
@@ -1442,19 +1424,11 @@
       <c r="F17" s="14" t="n"/>
     </row>
     <row r="18" customFormat="1" s="25">
-      <c r="A18" s="85" t="inlineStr">
-        <is>
-          <t>Передає: позаштатний начальник складу взводу матеріально-технічного забезпечення 6 батальйону ТрО, старший сержант Андрій ПЕТРЕНКО</t>
-        </is>
-      </c>
+      <c r="A18" s="85"/>
       <c r="B18" s="23" t="n"/>
       <c r="C18" s="14" t="n"/>
       <c r="D18" s="14" t="n"/>
-      <c r="E18" s="85" t="inlineStr">
-        <is>
-          <t>Приймає: господарчий взвод роти логістики</t>
-        </is>
-      </c>
+      <c r="E18" s="85"/>
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="25" t="n"/>
     </row>
@@ -1565,24 +1539,12 @@
       <c r="A23" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Виробничий стіл з реж.сталі 1500*600, 1113001082</t>
-        </is>
-      </c>
+      <c r="B23" s="19"/>
       <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
+      <c r="D23" s="18"/>
       <c r="E23" s="18" t="n"/>
-      <c r="F23" s="43" t="n">
-        <v>4914</v>
-      </c>
-      <c r="G23" s="44" t="n">
-        <v>4</v>
-      </c>
+      <c r="F23" s="43"/>
+      <c r="G23" s="44"/>
       <c r="H23" s="20">
         <f>G23</f>
         <v/>
@@ -1594,9 +1556,7 @@
       <c r="J23" s="18" t="n"/>
     </row>
     <row r="24" hidden="1" ht="18.6" customFormat="1" customHeight="1" s="1" thickBot="1">
-      <c r="A24" s="61" t="n">
-        <v>2</v>
-      </c>
+      <c r="A24" s="61"/>
       <c r="B24" s="19" t="n"/>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="18" t="n"/>
@@ -1614,9 +1574,7 @@
       <c r="J24" s="18" t="n"/>
     </row>
     <row r="25" hidden="1" ht="18.6" customFormat="1" customHeight="1" s="1" thickBot="1">
-      <c r="A25" s="61" t="n">
-        <v>3</v>
-      </c>
+      <c r="A25" s="61"/>
       <c r="B25" s="19" t="n"/>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="18" t="n"/>
@@ -1791,20 +1749,12 @@
           <t xml:space="preserve">здав: </t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
-        <is>
-          <t>позаштатний начальник складу взводу матеріально-технічного забезпечення 6 батальйону ТрО</t>
-        </is>
-      </c>
+      <c r="B38" s="26"/>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="28" t="n"/>
       <c r="E38" s="28" t="n"/>
       <c r="F38" s="28" t="n"/>
-      <c r="G38" s="90" t="inlineStr">
-        <is>
-          <t>Андрій ПЕТРЕНКО</t>
-        </is>
-      </c>
+      <c r="G38" s="90"/>
       <c r="H38" s="107" t="n"/>
       <c r="I38" s="107" t="n"/>
       <c r="J38" s="107" t="n"/>
@@ -2005,11 +1955,7 @@
     </row>
     <row r="59" customFormat="1" s="25">
       <c r="A59" s="35" t="n"/>
-      <c r="B59" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                                        ______________                         Андрій БУК                </t>
-        </is>
-      </c>
+      <c r="B59" s="85"/>
     </row>
     <row r="60" customFormat="1" s="25">
       <c r="A60" s="85" t="n"/>
